--- a/data/trans_dic/IP07_R-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP07_R-Clase-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>82,19%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>82,87%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>85,1%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>77,55%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>81,96%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>76,33%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>83,93%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>76,95%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>82,19%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>82,87%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>85,1%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>77,7%</t>
+          <t>75,84%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>77,38%</t>
+          <t>76,77%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>75,63; 87,78</t>
+          <t>75,78; 87,87</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>68,26; 83,64</t>
+          <t>75,71; 88,46</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>76,53; 89,46</t>
+          <t>78,94; 90,83</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>69,54; 83,85</t>
+          <t>70,25; 84,16</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>74,86; 87,71</t>
+          <t>75,89; 88,02</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>75,82; 89,18</t>
+          <t>67,84; 82,94</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>78,2; 90,75</t>
+          <t>76,44; 89,68</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>68,63; 84,35</t>
+          <t>68,37; 82,2</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>76,95; 86,17</t>
+          <t>77,49; 86,01</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>74,38; 84,25</t>
+          <t>74,27; 84,56</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>79,87; 88,56</t>
+          <t>80,02; 88,58</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>71,84; 81,95</t>
+          <t>71,33; 81,37</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>82,54%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>81,46%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>86,23%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>81,58%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>74,91%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>75,83%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>93,91%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>74,46%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>82,54%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>81,46%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>86,23%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>81,77%</t>
+          <t>74,42%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>78,13%</t>
+          <t>77,9%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>66,59; 81,37</t>
+          <t>75,03; 88,7</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>68,43; 82,6</t>
+          <t>73,4; 87,26</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>88,91; 97,12</t>
+          <t>80,05; 90,56</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>65,68; 81,36</t>
+          <t>73,37; 87,62</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>75,67; 88,48</t>
+          <t>67,55; 81,78</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>74,47; 87,13</t>
+          <t>67,82; 82,08</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>80,29; 90,97</t>
+          <t>88,66; 97,09</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>72,85; 87,39</t>
+          <t>66,3; 81,1</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>73,61; 83,36</t>
+          <t>73,67; 83,73</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>73,56; 83,38</t>
+          <t>73,61; 83,23</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>85,93; 92,84</t>
+          <t>86,39; 93,14</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>72,15; 83,0</t>
+          <t>72,44; 82,5</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>75,26%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>76,99%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>92,2%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>82,13%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>79,37%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>77,49%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>88,93%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>84,15%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>75,26%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>76,99%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>92,2%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>82,21%</t>
+          <t>85,12%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>83,08%</t>
+          <t>83,58%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>70,62; 86,31</t>
+          <t>68,07; 82,11</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>68,74; 83,61</t>
+          <t>68,85; 83,59</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>80,7; 94,42</t>
+          <t>85,45; 95,82</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>74,89; 90,88</t>
+          <t>71,92; 89,79</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>68,31; 81,84</t>
+          <t>69,87; 86,43</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>68,97; 83,37</t>
+          <t>69,05; 84,16</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>85,18; 95,79</t>
+          <t>79,8; 93,88</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>72,04; 90,06</t>
+          <t>75,97; 92,39</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>70,82; 81,54</t>
+          <t>71,19; 81,87</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>71,72; 82,44</t>
+          <t>71,24; 81,91</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>86,21; 94,33</t>
+          <t>86,09; 94,36</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>75,87; 88,12</t>
+          <t>77,07; 88,87</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>77,38%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>70,97%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>86,42%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>76,59%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>78,43%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>71,95%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>83,58%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>78,38%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>77,38%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>70,97%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>86,42%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>76,54%</t>
+          <t>76,26%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>77,46%</t>
+          <t>76,44%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>73,4; 82,63</t>
+          <t>71,91; 81,71</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>66,9; 76,9</t>
+          <t>65,77; 75,8</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>79,53; 87,4</t>
+          <t>82,28; 89,99</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>71,88; 86,25</t>
+          <t>70,49; 81,7</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>71,81; 81,14</t>
+          <t>73,53; 82,49</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>66,04; 75,98</t>
+          <t>66,57; 77,12</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>82,15; 90,04</t>
+          <t>79,39; 87,37</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>70,96; 81,78</t>
+          <t>70,67; 80,98</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>74,14; 81,27</t>
+          <t>74,39; 81,13</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>67,79; 74,92</t>
+          <t>67,38; 74,85</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>81,82; 87,54</t>
+          <t>82,07; 87,62</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>72,66; 82,06</t>
+          <t>72,54; 79,76</t>
         </is>
       </c>
     </row>
@@ -1209,42 +1209,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>71,13%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>71,82%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>82,45%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>68,47%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>76,44%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>79,69%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>85,31%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>78,74%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>71,13%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>71,82%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>82,45%</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>68,95%</t>
+          <t>78,79%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>73,1%</t>
+          <t>73,06%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>69,5; 82,59</t>
+          <t>64,77; 77,33</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>73,76; 84,69</t>
+          <t>64,78; 77,45</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>79,27; 89,5</t>
+          <t>76,55; 87,87</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>71,61; 83,95</t>
+          <t>52,9; 75,82</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>64,48; 77,32</t>
+          <t>69,45; 82,96</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>65,26; 77,91</t>
+          <t>74,2; 84,96</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>76,22; 87,39</t>
+          <t>80,08; 89,63</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>53,82; 76,9</t>
+          <t>71,66; 83,9</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>68,43; 77,65</t>
+          <t>68,57; 77,79</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>71,29; 79,75</t>
+          <t>71,45; 79,95</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>79,96; 86,97</t>
+          <t>79,51; 87,19</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>63,35; 78,16</t>
+          <t>64,28; 77,81</t>
         </is>
       </c>
     </row>
@@ -1349,42 +1349,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>73,75%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>78,14%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>84,43%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>73,94%</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>76,65%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>71,07%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>89,73%</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>73,33%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>73,75%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>78,14%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>84,43%</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>75,9%</t>
+          <t>72,76%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>74,64%</t>
+          <t>73,34%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>68,81; 84,13</t>
+          <t>65,01; 81,7</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>59,44; 80,81</t>
+          <t>69,17; 85,15</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>80,76; 95,32</t>
+          <t>75,6; 90,13</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>64,06; 81,33</t>
+          <t>63,19; 82,92</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>65,95; 81,77</t>
+          <t>67,88; 83,69</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>68,02; 85,73</t>
+          <t>60,47; 80,94</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>76,53; 90,91</t>
+          <t>80,73; 94,77</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>65,56; 84,85</t>
+          <t>62,62; 80,81</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>69,17; 80,92</t>
+          <t>68,63; 80,35</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>67,0; 80,98</t>
+          <t>68,01; 80,71</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>80,76; 91,22</t>
+          <t>80,55; 91,36</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>67,91; 80,53</t>
+          <t>65,94; 79,7</t>
         </is>
       </c>
     </row>
@@ -1489,42 +1489,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>76,86%</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>75,52%</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>85,83%</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>75,87%</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>78,09%</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>75,4%</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>86,64%</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>77,58%</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>76,86%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>75,52%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>85,83%</t>
-        </is>
-      </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>76,19%</t>
+          <t>76,76%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>76,84%</t>
+          <t>76,29%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>75,22; 80,51</t>
+          <t>74,34; 79,68</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>72,4; 77,88</t>
+          <t>72,69; 77,89</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>84,3; 88,71</t>
+          <t>83,59; 88,04</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>74,4; 81,03</t>
+          <t>72,18; 79,01</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>73,88; 79,21</t>
+          <t>75,29; 80,67</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>72,81; 78,06</t>
+          <t>72,64; 77,94</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>83,64; 87,98</t>
+          <t>84,34; 88,58</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>71,62; 79,42</t>
+          <t>73,85; 79,46</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>75,48; 79,11</t>
+          <t>75,51; 79,2</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>73,54; 77,37</t>
+          <t>73,46; 77,2</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>84,67; 87,77</t>
+          <t>84,69; 87,75</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>74,24; 79,18</t>
+          <t>73,78; 78,38</t>
         </is>
       </c>
     </row>
@@ -1675,7 +1675,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1683,7 +1683,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1791,42 +1791,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>108</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>135</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>125</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>99</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>103</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>119</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>108</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>123</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>135</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1859,42 +1859,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>80175</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>74387</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>84380</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>95051</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>85523</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>68088</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>68565</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>80380</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>80175</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>74387</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>84380</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>106382</t>
+          <t>78061</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>186762</t>
+          <t>173114</t>
         </is>
       </c>
     </row>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>78926; 91601</t>
+          <t>73923; 85711</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>60889; 74602</t>
+          <t>67957; 79403</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>62513; 73081</t>
+          <t>78273; 90062</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>72640; 87595</t>
+          <t>86107; 103155</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>73022; 85554</t>
+          <t>79197; 91855</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>68060; 80048</t>
+          <t>60513; 73979</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>77534; 89978</t>
+          <t>62441; 73263</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>93956; 115476</t>
+          <t>70373; 84602</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>155357; 173977</t>
+          <t>156448; 173643</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>133107; 150776</t>
+          <t>132907; 151323</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>144444; 160158</t>
+          <t>144709; 160185</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>173410; 197797</t>
+          <t>160853; 183480</t>
         </is>
       </c>
     </row>
@@ -1999,42 +1999,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>141</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>108</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>97</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>102</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>145</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>104</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>106</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>113</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>141</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>108</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -2067,42 +2067,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>70407</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>78294</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>96557</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>74566</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>65467</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>70721</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>98196</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>70499</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>70407</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>78294</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>96557</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>78147</t>
+          <t>71849</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>148647</t>
+          <t>146415</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>58194; 71109</t>
+          <t>64004; 75664</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>63818; 77040</t>
+          <t>70544; 83867</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>92966; 101553</t>
+          <t>89637; 101410</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>62186; 77029</t>
+          <t>67062; 80087</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>64547; 75480</t>
+          <t>59031; 71467</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>71574; 83741</t>
+          <t>63254; 76552</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>89908; 101865</t>
+          <t>92710; 101524</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>69629; 83524</t>
+          <t>64014; 78303</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>127113; 143961</t>
+          <t>127224; 144586</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>139297; 157909</t>
+          <t>139397; 157622</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>186069; 201039</t>
+          <t>187073; 201698</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>137264; 157907</t>
+          <t>136153; 155051</t>
         </is>
       </c>
     </row>
@@ -2207,42 +2207,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>80</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>97</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>85</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>62</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>111</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>96</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>102</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>69</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -2275,42 +2275,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>74755</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>66894</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>69548</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>46766</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>53490</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>66219</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>54993</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>43643</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>74755</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>66894</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>69548</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>52494</t>
+          <t>45522</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>96137</t>
+          <t>92288</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>47591; 58164</t>
+          <t>67616; 81557</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>58740; 71455</t>
+          <t>59823; 72635</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>49906; 58391</t>
+          <t>64449; 72278</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>38838; 47133</t>
+          <t>40952; 51125</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>67857; 81293</t>
+          <t>47090; 58246</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>59929; 72443</t>
+          <t>59009; 71926</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>64247; 72251</t>
+          <t>49351; 58053</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>45997; 57507</t>
+          <t>40632; 49415</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>118076; 135951</t>
+          <t>118691; 136500</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>123602; 142078</t>
+          <t>122785; 141174</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>118337; 129480</t>
+          <t>118177; 129530</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>87788; 101973</t>
+          <t>85103; 98137</t>
         </is>
       </c>
     </row>
@@ -2415,42 +2415,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>235</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>229</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>261</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>214</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>238</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>215</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>284</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>210</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>235</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>229</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>261</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>214</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2483,42 +2483,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>155210</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>161381</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>182223</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>154674</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>157433</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>147734</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>186372</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>171522</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>155210</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>161381</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>182223</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>167060</t>
+          <t>137016</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>338583</t>
+          <t>291690</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>147336; 165862</t>
+          <t>144234; 163886</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>137355; 157883</t>
+          <t>149546; 172349</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>177337; 194885</t>
+          <t>173488; 189739</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>157284; 188734</t>
+          <t>142344; 164990</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>144032; 162755</t>
+          <t>147595; 165592</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>150169; 172779</t>
+          <t>136692; 158336</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>173222; 189857</t>
+          <t>177023; 194806</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>154880; 178513</t>
+          <t>126966; 145486</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>297511; 326128</t>
+          <t>298517; 325567</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>293331; 324168</t>
+          <t>291538; 323892</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>354950; 379790</t>
+          <t>356043; 380136</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>317594; 358670</t>
+          <t>276826; 304383</t>
         </is>
       </c>
     </row>
@@ -2623,42 +2623,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>136</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>141</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>165</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>142</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>118</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>170</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>175</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>139</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>136</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>141</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>165</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>142</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2691,42 +2691,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>90080</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>100186</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>117972</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>101499</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>79585</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>118873</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>116182</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>94034</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>90080</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>100186</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>117972</t>
-        </is>
-      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>112129</t>
+          <t>93549</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>206163</t>
+          <t>195047</t>
         </is>
       </c>
     </row>
@@ -2759,62 +2759,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>72364; 85990</t>
+          <t>82034; 97937</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>110026; 126327</t>
+          <t>90371; 108047</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>107955; 121891</t>
+          <t>109528; 125735</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>85524; 100259</t>
+          <t>78427; 112404</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>81657; 97919</t>
+          <t>72316; 86375</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>91043; 108688</t>
+          <t>110683; 126727</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>109056; 125050</t>
+          <t>109069; 122071</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>87528; 125054</t>
+          <t>85078; 99618</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>157925; 179201</t>
+          <t>158248; 179516</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>205794; 230210</t>
+          <t>206245; 230796</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>223317; 242886</t>
+          <t>222062; 243506</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>178686; 220435</t>
+          <t>171624; 207736</t>
         </is>
       </c>
     </row>
@@ -2831,42 +2831,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
           <t>84</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>55</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="I19" s="2" t="inlineStr">
         <is>
           <t>79</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="J19" s="2" t="inlineStr">
         <is>
           <t>71</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>69</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -2899,42 +2899,42 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>53391</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>57292</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>56597</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>50493</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
           <t>57390</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>38315</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>53514</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>50522</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>53391</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>57292</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>56597</t>
-        </is>
-      </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>54648</t>
+          <t>51194</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>105170</t>
+          <t>101688</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>51519; 62989</t>
+          <t>47061; 59145</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>32046; 43563</t>
+          <t>50713; 62432</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>48165; 56850</t>
+          <t>50678; 60418</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>44131; 56030</t>
+          <t>43153; 56625</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>47742; 59194</t>
+          <t>50822; 62655</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>49870; 62855</t>
+          <t>32598; 43635</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>51300; 60941</t>
+          <t>48147; 56521</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>47206; 61093</t>
+          <t>44054; 56852</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>101861; 119164</t>
+          <t>101066; 118323</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>85246; 103037</t>
+          <t>86530; 102686</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>102303; 115550</t>
+          <t>102034; 115734</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>95686; 113471</t>
+          <t>91420; 110500</t>
         </is>
       </c>
     </row>
@@ -3039,42 +3039,42 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>788</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>771</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>873</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>737</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
           <t>742</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>738</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="I22" s="2" t="inlineStr">
         <is>
           <t>871</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="J22" s="2" t="inlineStr">
         <is>
           <t>705</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>788</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>771</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>873</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>737</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -3107,42 +3107,42 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>524018</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>538435</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>607276</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>523049</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
           <t>498887</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>509950</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="I23" s="2" t="inlineStr">
         <is>
           <t>577822</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>510601</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>524018</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>538435</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>607276</t>
-        </is>
-      </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>570859</t>
+          <t>477192</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>1081460</t>
+          <t>1000242</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>480579; 514312</t>
+          <t>506871; 543223</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>489635; 526735</t>
+          <t>518245; 555328</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>562205; 591610</t>
+          <t>591459; 622918</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>489672; 533326</t>
+          <t>497603; 544680</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>503732; 540018</t>
+          <t>481020; 515340</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>519146; 556554</t>
+          <t>491296; 527106</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>591802; 622474</t>
+          <t>562436; 590738</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>536563; 595007</t>
+          <t>459155; 494009</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>996862; 1044815</t>
+          <t>997236; 1045963</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1021701; 1074883</t>
+          <t>1020535; 1072583</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>1163802; 1206363</t>
+          <t>1164033; 1206025</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>1044786; 1114392</t>
+          <t>967277; 1027580</t>
         </is>
       </c>
     </row>
